--- a/Wyniki/next push.xlsx
+++ b/Wyniki/next push.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\RackIT\Wyniki\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF206E9B-604E-4924-957F-0F29C251C7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EBFCBA-9575-4B2F-A049-F46747DF002D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUSH – Klatka · Barki · Triceps" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="74">
   <si>
     <t>PUSH – Klatka · Barki · Triceps</t>
   </si>
@@ -110,18 +110,12 @@
     <t>RIR 2  –  7–8 powt., 2 w zapasie</t>
   </si>
   <si>
-    <t>RIR 1  –  6–7 powt., 1 w zapasie</t>
-  </si>
-  <si>
     <t>piramida – każda seria ciężej</t>
   </si>
   <si>
     <t>Wyciskanie hantlami – skośna +30°</t>
   </si>
   <si>
-    <t>8–10</t>
-  </si>
-  <si>
     <t>2 × 25 kg</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>OHP sztangą</t>
   </si>
   <si>
-    <t>30 kg</t>
-  </si>
-  <si>
     <t>RIR 3  –  7–8 powt., 3 w zapasie</t>
   </si>
   <si>
@@ -260,10 +251,16 @@
     <t>RIR 0  –  DO UPADKU min 9</t>
   </si>
   <si>
-    <t>RIR 0  –  DO UPADKU min 11</t>
-  </si>
-  <si>
     <t>7,5</t>
+  </si>
+  <si>
+    <t>RIR 1  –  6–7 powt., 1 w zapasie min 8</t>
+  </si>
+  <si>
+    <t>RIR 0  –  DO UPADKU min 8</t>
+  </si>
+  <si>
+    <t>6-8</t>
   </si>
 </sst>
 </file>
@@ -662,30 +659,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -698,10 +698,7 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="10" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -946,7 +943,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="30"/>
@@ -970,7 +967,7 @@
       <c r="T1" s="30"/>
     </row>
     <row r="2" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="30"/>
@@ -996,7 +993,7 @@
     <row r="3" spans="1:24" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:24" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="33" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="30"/>
@@ -1029,23 +1026,23 @@
       <c r="G6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="32"/>
-      <c r="I6" s="33"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="36"/>
       <c r="J6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="32"/>
-      <c r="L6" s="33"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="36"/>
       <c r="M6" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="32"/>
-      <c r="O6" s="33"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="36"/>
       <c r="P6" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="33"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="36"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
     </row>
@@ -1149,7 +1146,7 @@
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="10" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="P8" s="5">
         <v>77.5</v>
@@ -1163,7 +1160,7 @@
         <v>–</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -1171,40 +1168,40 @@
         <v>2</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" s="15">
         <v>3</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>26</v>
+      <c r="D9" s="15">
+        <v>8</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H9" s="15"/>
-      <c r="I9" s="9" t="s">
-        <v>29</v>
+      <c r="I9" s="9">
+        <v>8</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K9" s="15"/>
-      <c r="L9" s="10" t="s">
-        <v>30</v>
+      <c r="L9" s="10">
+        <v>8</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N9" s="15"/>
-      <c r="O9" s="11" t="s">
-        <v>73</v>
+      <c r="O9" s="11">
+        <v>8</v>
       </c>
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
@@ -1214,7 +1211,7 @@
         <v>–</v>
       </c>
       <c r="T9" s="18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -1222,47 +1219,47 @@
         <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
       </c>
-      <c r="D10" s="44">
-        <v>46240</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>33</v>
+      <c r="D10" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="6">
+        <v>35</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G10" s="5">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J10" s="5">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M10" s="5">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P10" s="5">
         <v>45</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="S10" s="5" t="str">
         <f>IF(Q10="","–",IF(ISNUMBER(Q10),IF(Q10&gt;10,"✓ TAK – dodaj 2,5 kg","✗ NIE – zostań z ciężarem"),"–"))</f>
@@ -1275,16 +1272,16 @@
         <v>4</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" s="15">
         <v>3</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E11" s="16">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>20</v>
@@ -1294,21 +1291,21 @@
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J11" s="15">
         <v>7.5</v>
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
@@ -1318,7 +1315,7 @@
         <v>–</v>
       </c>
       <c r="T11" s="18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -1326,16 +1323,16 @@
         <v>5</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C12" s="5">
         <v>4</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>20</v>
@@ -1345,43 +1342,43 @@
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J12" s="5">
         <v>-9.4</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M12" s="5">
         <v>-6.25</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="S12" s="5" t="str">
         <f>IF(Q12="","–",IF(ISNUMBER(Q12),IF(Q12&gt;12,"✓ TAK – dodaj 2,5 kg","✗ NIE – zostań z ciężarem"),"–"))</f>
         <v>–</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="X12" s="20">
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
-        <v>49</v>
+      <c r="A13" s="37" t="s">
+        <v>46</v>
       </c>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -1404,8 +1401,8 @@
       <c r="T13" s="30"/>
     </row>
     <row r="15" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
-        <v>50</v>
+      <c r="A15" s="29" t="s">
+        <v>47</v>
       </c>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -1429,187 +1426,187 @@
     </row>
     <row r="16" spans="1:24" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="33"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="36"/>
       <c r="T16" s="22"/>
     </row>
     <row r="17" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="33"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="36"/>
       <c r="T17" s="25"/>
     </row>
     <row r="18" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
+        <v>52</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="36"/>
       <c r="F18" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="33"/>
+        <v>57</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="36"/>
       <c r="T18" s="28"/>
     </row>
     <row r="19" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="32"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="33"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="36"/>
       <c r="T19" s="25"/>
     </row>
     <row r="20" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="33"/>
+        <v>59</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="36"/>
       <c r="F20" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="33"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="36"/>
       <c r="T20" s="28"/>
     </row>
     <row r="21" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
+        <v>65</v>
+      </c>
+      <c r="B21" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="36"/>
       <c r="F21" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="32"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="33"/>
+        <v>61</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="36"/>
       <c r="T21" s="25"/>
     </row>
     <row r="22" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
-        <v>71</v>
+      <c r="A22" s="38" t="s">
+        <v>68</v>
       </c>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -2611,12 +2608,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A15:T15"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="A5:T5"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="A13:T13"/>
     <mergeCell ref="A22:T22"/>
     <mergeCell ref="G16:S16"/>
     <mergeCell ref="M6:O6"/>
@@ -2633,6 +2624,12 @@
     <mergeCell ref="G18:S18"/>
     <mergeCell ref="G17:S17"/>
     <mergeCell ref="B19:E19"/>
+    <mergeCell ref="A15:T15"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="A13:T13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape"/>

--- a/Wyniki/next push.xlsx
+++ b/Wyniki/next push.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PUSH – Klatka · Barki · Triceps" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PUSH – Klatka · Barki · Triceps" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>2x22,5</t>
+          <t>2x25</t>
         </is>
       </c>
       <c r="K9" s="15" t="n"/>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-9.4</v>
+        <v>-6.25</v>
       </c>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="8" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>-9.4</v>
+        <v>-6.25</v>
       </c>
       <c r="K12" s="5" t="n"/>
       <c r="L12" s="9" t="inlineStr">
